--- a/data/trans_camb/P16A06-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A06-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 0,56</t>
+          <t>-2,59; 0,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,01; 4,25</t>
+          <t>0,1; 4,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,54; 10,88</t>
+          <t>4,96; 10,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,35</t>
+          <t>1,04; 5,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,36; 10,88</t>
+          <t>5,31; 10,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,52; 18,51</t>
+          <t>12,6; 18,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 2,83</t>
+          <t>-0,08; 2,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,72; 7,27</t>
+          <t>3,66; 7,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,5; 14,56</t>
+          <t>10,58; 14,52</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-57,37; 18,06</t>
+          <t>-56,67; 18,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 133,82</t>
+          <t>1,35; 144,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>118,84; 357,52</t>
+          <t>112,19; 359,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,77; 87,6</t>
+          <t>13,19; 86,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>65,95; 182,69</t>
+          <t>66,19; 175,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>155,76; 298,43</t>
+          <t>152,67; 299,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 57,88</t>
+          <t>-1,15; 59,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>58,52; 141,64</t>
+          <t>60,07; 144,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>164,58; 293,06</t>
+          <t>165,08; 294,79</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,32</t>
+          <t>-0,25; 1,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 1,25</t>
+          <t>-0,29; 1,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,5</t>
+          <t>1,06; 3,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,19</t>
+          <t>0,55; 3,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,66</t>
+          <t>1,19; 3,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,81</t>
+          <t>2,58; 5,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,9</t>
+          <t>0,37; 1,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,15</t>
+          <t>0,62; 2,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,32</t>
+          <t>2,22; 4,26</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,48; 158,7</t>
+          <t>-21,77; 186,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-26,17; 151,73</t>
+          <t>-22,68; 162,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53,84; 405,87</t>
+          <t>68,92; 406,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,75; 155,97</t>
+          <t>16,66; 173,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,45; 190,73</t>
+          <t>33,22; 193,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,51; 288,09</t>
+          <t>89,4; 297,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,86; 128,33</t>
+          <t>14,92; 127,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28,37; 143,94</t>
+          <t>28,6; 147,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>109,8; 286,08</t>
+          <t>103,92; 280,87</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 2,94</t>
+          <t>-0,55; 3,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 2,6</t>
+          <t>-0,53; 2,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,88</t>
+          <t>1,39; 5,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 3,26</t>
+          <t>-1,14; 3,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 3,73</t>
+          <t>-0,11; 3,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,73</t>
+          <t>1,8; 5,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 2,48</t>
+          <t>-0,32; 2,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 2,65</t>
+          <t>0,06; 2,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,71</t>
+          <t>2,21; 4,73</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-59,38; 564,75</t>
+          <t>-55,87; 682,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-45,6; 595,78</t>
+          <t>-48,08; 518,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>59,11; 1086,78</t>
+          <t>57,77; 1044,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-49,57; 305,4</t>
+          <t>-50,53; 302,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-22,59; 382,43</t>
+          <t>-14,67; 424,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>47,31; 593,19</t>
+          <t>51,34; 633,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-35,36; 247,03</t>
+          <t>-22,8; 239,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,43; 298,8</t>
+          <t>0,47; 280,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>103,52; 567,52</t>
+          <t>96,71; 540,62</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 0,73</t>
+          <t>-0,69; 0,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 1,37</t>
+          <t>-0,11; 1,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,91</t>
+          <t>1,55; 3,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,19</t>
+          <t>0,96; 3,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,48</t>
+          <t>2,23; 4,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,82; 6,95</t>
+          <t>3,7; 6,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,76</t>
+          <t>0,43; 1,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 2,72</t>
+          <t>1,37; 2,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,28; 5,15</t>
+          <t>3,25; 5,12</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-27,49; 44,43</t>
+          <t>-30,1; 48,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 79,38</t>
+          <t>-5,28; 83,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74,09; 231,24</t>
+          <t>65,79; 226,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21,65; 85,1</t>
+          <t>20,24; 87,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>47,0; 121,02</t>
+          <t>48,38; 119,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>86,47; 188,77</t>
+          <t>88,45; 188,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,77; 61,14</t>
+          <t>12,97; 61,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>40,8; 98,55</t>
+          <t>40,81; 98,45</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>100,9; 186,13</t>
+          <t>100,22; 185,23</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A06-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A06-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7,94</t>
+          <t>7,2</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,36</t>
+          <t>14,62</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12,46</t>
+          <t>11,64</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,4</t>
+          <t>-2,51; 0,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 4,21</t>
+          <t>0,11; 4,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,96; 10,59</t>
+          <t>4,89; 10,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 5,29</t>
+          <t>0,96; 5,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,31; 10,94</t>
+          <t>5,1; 10,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,6; 18,25</t>
+          <t>12,12; 17,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 2,92</t>
+          <t>-0,03; 2,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,66; 7,14</t>
+          <t>3,59; 7,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,58; 14,52</t>
+          <t>9,94; 13,49</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>210,91%</t>
+          <t>191,19%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>217,79%</t>
+          <t>207,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>222,2%</t>
+          <t>207,54%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-56,67; 18,44</t>
+          <t>-56,42; 19,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 144,29</t>
+          <t>1,35; 138,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>112,19; 359,71</t>
+          <t>102,72; 329,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,19; 86,98</t>
+          <t>10,51; 82,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>66,19; 175,5</t>
+          <t>59,87; 170,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>152,67; 299,53</t>
+          <t>144,42; 281,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 59,24</t>
+          <t>-0,55; 53,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>60,07; 144,5</t>
+          <t>56,14; 144,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>165,08; 294,79</t>
+          <t>156,56; 267,39</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,36</t>
+          <t>2,87</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,39</t>
+          <t>5,25</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,38</t>
+          <t>4,05</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,43</t>
+          <t>-0,39; 1,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,35</t>
+          <t>-0,44; 1,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,38</t>
+          <t>1,88; 3,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,23</t>
+          <t>0,39; 3,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,76</t>
+          <t>1,1; 3,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,58; 5,86</t>
+          <t>3,94; 6,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,87</t>
+          <t>0,37; 1,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,15</t>
+          <t>0,65; 2,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,26</t>
+          <t>3,24; 4,92</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>195,4%</t>
+          <t>237,52%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>177,79%</t>
+          <t>212,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>185,65%</t>
+          <t>222,75%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-21,77; 186,63</t>
+          <t>-26,39; 161,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-22,68; 162,43</t>
+          <t>-29,37; 138,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68,92; 406,51</t>
+          <t>96,43; 460,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,66; 173,08</t>
+          <t>11,7; 156,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,22; 193,72</t>
+          <t>33,67; 186,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,4; 297,98</t>
+          <t>122,44; 363,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,92; 127,73</t>
+          <t>16,51; 126,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28,6; 147,15</t>
+          <t>27,91; 145,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>103,92; 280,87</t>
+          <t>141,51; 334,39</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,0</t>
+          <t>2,86</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,82</t>
+          <t>3,83</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,45</t>
+          <t>3,39</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,03</t>
+          <t>-0,57; 3,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 2,52</t>
+          <t>-0,49; 2,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,39; 5,13</t>
+          <t>1,28; 4,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 3,02</t>
+          <t>-0,94; 3,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 3,91</t>
+          <t>-0,5; 3,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,8; 5,75</t>
+          <t>1,79; 5,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 2,52</t>
+          <t>-0,35; 2,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 2,56</t>
+          <t>-0,04; 2,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,73</t>
+          <t>2,16; 4,72</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>293,3%</t>
+          <t>279,65%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>209,88%</t>
+          <t>210,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>247,6%</t>
+          <t>243,31%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-55,87; 682,87</t>
+          <t>-57,76; 519,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-48,08; 518,48</t>
+          <t>-50,05; 465,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>57,77; 1044,19</t>
+          <t>62,38; 896,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-50,53; 302,48</t>
+          <t>-46,04; 356,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-14,67; 424,83</t>
+          <t>-27,43; 334,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>51,34; 633,48</t>
+          <t>46,19; 586,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-22,8; 239,39</t>
+          <t>-25,66; 244,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,47; 280,09</t>
+          <t>-4,53; 288,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>96,71; 540,62</t>
+          <t>98,6; 544,43</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,88</t>
+          <t>3,18</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,68</t>
+          <t>6,22</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,34</t>
+          <t>4,76</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,8</t>
+          <t>-0,72; 0,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1335,37 +1335,37 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,78</t>
+          <t>2,26; 4,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,21</t>
+          <t>1,0; 3,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,23; 4,41</t>
+          <t>2,23; 4,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,7; 6,97</t>
+          <t>5,21; 7,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,71</t>
+          <t>0,4; 1,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,76</t>
+          <t>1,37; 2,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,25; 5,12</t>
+          <t>4,04; 5,48</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>145,33%</t>
+          <t>160,59%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>136,55%</t>
+          <t>149,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>140,32%</t>
+          <t>153,97%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-30,1; 48,38</t>
+          <t>-31,0; 46,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 83,58</t>
+          <t>-5,41; 82,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>65,79; 226,97</t>
+          <t>95,69; 247,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20,24; 87,02</t>
+          <t>20,38; 86,3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>48,38; 119,27</t>
+          <t>46,83; 122,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>88,45; 188,79</t>
+          <t>109,87; 202,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,97; 61,13</t>
+          <t>12,01; 62,96</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>40,81; 98,45</t>
+          <t>40,73; 97,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>100,22; 185,23</t>
+          <t>115,73; 198,76</t>
         </is>
       </c>
     </row>
